--- a/02_加值成品/八上/八上2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-3 混合物的分離　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上2-3 混合物的分離　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>分離不溶固體與液體用？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>濾紙</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>分液(傾析)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>蒸餾</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>過濾</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>顆粒差異</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>海水取鹽用什麼方法？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>蒸發結晶</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>分液(傾析)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不溶固體</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>溶劑蒸發</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>利用沸點差異分離液體用？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>蒸餾</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>海水淡化</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>冷凝</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>汽化冷凝</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>分離混合色素用？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>分液(傾析)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>濾紙層析</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>蒸發結晶</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>海水淡化</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>移動速率差</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>過濾後留在濾紙上的是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>蒸發結晶</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>不溶固體</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>被擋住</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>蒸餾中蒸氣冷卻變回液體叫？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>冷凝</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>蒸餾</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>蒸發結晶</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>不溶固體</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>放熱</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>曬鹽利用哪種方法？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>蒸發</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>濾紙層析</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>海水淡化</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>日曬</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>過濾能分離溶解的糖嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>蒸餾</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>分液(傾析)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>冷凝</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>需蒸發</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>過濾用到的多孔紙張是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>濾紙</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>蒸發</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>分液(傾析)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>蒸發結晶</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>器材</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>把海水變飲用水的處理稱？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>濾紙層析</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>蒸發結晶</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>冷凝</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>海水淡化</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>淡化</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-3 混合物的分離　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上2-3 混合物的分離　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>分離泥沙與水用？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>過濾</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>分液(傾析)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>濾紙層析</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>蒸發</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>沙不溶</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>分離酒精與水用？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>蒸餾</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>不溶固體</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>濾紙層析</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>沸點不同</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>鹽水蒸乾得到？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>鹽</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>冷凝</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>濾紙</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>過濾</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>水蒸發</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>蒸餾收集到的液體是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>導電性低、沸點固定</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>不可浸入溶劑中</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>水汽化冷凝、雜質留下</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>純化的溶劑(水)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>冷凝液</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>層析中跑得快的成分表示？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>水汽化冷凝、雜質留下</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>不溶固體/溶解固體/水</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>導電性低、沸點固定</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>與濾紙作用弱、移動快</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>分離依據</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>要同時取得水和鹽用？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>不溶固體</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>蒸發結晶</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>蒸餾</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>冷凝取水、殘留取鹽</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>過濾裝置需要哪些器材？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>不溶固體</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>分液(傾析)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>漏斗與濾紙</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>過濾</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>基本組</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>海水淡化常用原理近似？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>蒸發結晶</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>蒸餾</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>液體受熱汽化</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>鹽</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>汽化再凝</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>分離糖水中的糖用什麼方法？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>液體受熱汽化</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>蒸發結晶</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>蒸餾</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>酒精</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>溶劑蒸發</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>蒸餾過程中先發生什麼？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>蒸發</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>不溶固體</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>液體受熱汽化</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>分液(傾析)</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>汽化</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上2-3 混合物的分離　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上2-3 混合物的分離　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>鹽和沙的混合物如何分離？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>純化的溶劑(水)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>加水溶鹽→過濾→蒸發</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>濾紙層析,各色素移動速率不同</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>水汽化冷凝、雜質留下</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>兩步驟</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何蒸餾能得純水？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>純化的溶劑(水)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>溶解過濾再蒸發</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>導電性低、沸點固定</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>水汽化冷凝、雜質留下</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>分離沸點</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>層析為何色素會分開？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>各成分移動速率不同</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>水汽化冷凝、雜質留下</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>導電性低、沸點固定</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不溶固體/溶解固體/水</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>速率差</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>分離不互溶的油和水最簡便法？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>冷凝</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>酒精</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>蒸餾</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>分液(傾析)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>密度分層</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>先過濾再蒸發能分離哪三者？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>不溶固體/溶解固體/水</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>加水溶鹽→過濾→蒸發</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>水汽化冷凝、雜質留下</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>與濾紙作用弱、移動快</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>逐步</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>墨水點在濾紙下端要注意？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>各成分移動速率不同</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>濾紙層析,各色素移動速率不同</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>不可浸入溶劑中</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>水汽化冷凝、雜質留下</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>避免溶掉</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>酒精沸點78℃、水100℃先蒸出？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>蒸餾</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>漏斗與濾紙</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>蒸發結晶</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>酒精</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>沸點低先汽化</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>如何驗證蒸餾水較純？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>導電性低、沸點固定</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>純化的溶劑(水)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>與濾紙作用弱、移動快</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>水汽化冷凝、雜質留下</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>性質檢驗</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>分析墨水色素成分用哪種方法?為何</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>濾紙層析,各色素移動速率不同</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>導電性低、沸點固定</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>與濾紙作用弱、移動快</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>純化的溶劑(水)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>層析</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>分離沙鹽水三者的步驟順序？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>溶解過濾再蒸發</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>各成分移動速率不同</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>與濾紙作用弱、移動快</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>不溶固體/溶解固體/水</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>步驟</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-3_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>濾紙</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>分液(傾析)</t>
+          <t>濾紙層析</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>蒸餾</t>
+          <t>冷凝</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -603,22 +603,22 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
+          <t>濾紙層析</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>蒸發結晶</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>鹽</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>蒸發結晶</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>分液(傾析)</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>不溶固體</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>海水淡化</t>
+          <t>不溶固體</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>冷凝</t>
+          <t>漏斗與濾紙</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>分液(傾析)</t>
+          <t>過濾</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>蒸發結晶</t>
+          <t>蒸餾</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>海水淡化</t>
+          <t>漏斗與濾紙</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -723,17 +723,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>漏斗與濾紙</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>蒸發結晶</t>
-        </is>
-      </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>鹽</t>
+          <t>過濾</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>蒸餾</t>
+          <t>蒸發結晶</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>蒸發結晶</t>
+          <t>濾紙層析</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>不溶固體</t>
+          <t>蒸發</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -808,17 +808,17 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>漏斗與濾紙</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>濾紙層析</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>不能</t>
-        </is>
-      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>海水淡化</t>
+          <t>蒸發結晶</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -843,17 +843,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>蒸餾</t>
+          <t>蒸發結晶</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>分液(傾析)</t>
+          <t>酒精</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>冷凝</t>
+          <t>蒸發</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>蒸發</t>
+          <t>蒸發結晶</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>分液(傾析)</t>
+          <t>漏斗與濾紙</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>蒸發結晶</t>
+          <t>酒精</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>濾紙層析</t>
+          <t>蒸餾</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>冷凝</t>
+          <t>漏斗與濾紙</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -1044,17 +1044,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>分液(傾析)</t>
+          <t>冷凝</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>濾紙層析</t>
+          <t>海水淡化</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>蒸發</t>
+          <t>蒸發結晶</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>蒸發結晶</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>冷凝</t>
+          <t>濾紙</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>濾紙</t>
+          <t>漏斗與濾紙</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>過濾</t>
+          <t>海水淡化</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>導電性低、沸點固定</t>
+          <t>不溶固體/溶解固體/水</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>水汽化冷凝、雜質留下</t>
+          <t>各成分移動速率不同</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -1194,37 +1194,37 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>層析中跑得快的成分表示？</t>
+          <t>層析後在濾紙上跑得比較遠的色素代表？</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>水汽化冷凝、雜質留下</t>
+          <t>隨溶劑移動速率較快</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>不溶固體/溶解固體/水</t>
+          <t>濾紙層析,各色素移動速率不同</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>導電性低、沸點固定</t>
+          <t>靜置後,倒出上層的油</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>與濾紙作用弱、移動快</t>
+          <t>純化的溶劑(水)</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>分離依據</t>
+          <t>移動較快</t>
         </is>
       </c>
     </row>
@@ -1239,17 +1239,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>鹽</t>
+          <t>漏斗與濾紙</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>不溶固體</t>
+          <t>海水淡化</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>蒸發結晶</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>不溶固體</t>
+          <t>過濾</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>分液(傾析)</t>
+          <t>酒精</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>過濾</t>
+          <t>蒸發結晶</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>蒸發結晶</t>
+          <t>過濾</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>液體受熱汽化</t>
+          <t>酒精</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>鹽</t>
+          <t>漏斗與濾紙</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>液體受熱汽化</t>
+          <t>海水淡化</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>蒸餾</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>酒精</t>
+          <t>冷凝</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>蒸發</t>
+          <t>過濾</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>不溶固體</t>
+          <t>濾紙</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>分液(傾析)</t>
+          <t>蒸發結晶</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>純化的溶劑(水)</t>
+          <t>隨溶劑移動速率較快</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>濾紙層析,各色素移動速率不同</t>
+          <t>不溶固體/溶解固體/水</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>水汽化冷凝、雜質留下</t>
+          <t>各成分移動速率不同</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>純化的溶劑(水)</t>
+          <t>溶解過濾再蒸發</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>溶解過濾再蒸發</t>
+          <t>各成分移動速率不同</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>導電性低、沸點固定</t>
+          <t>不可浸入溶劑中</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>水汽化冷凝、雜質留下</t>
+          <t>濾紙層析,各色素移動速率不同</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>導電性低、沸點固定</t>
+          <t>純化的溶劑(水)</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>不溶固體/溶解固體/水</t>
+          <t>加水溶鹽→過濾→蒸發</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1635,22 +1635,22 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>冷凝</t>
+          <t>濾紙層析,各色素移動速率不同</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>酒精</t>
+          <t>不可浸入溶劑中</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>蒸餾</t>
+          <t>隨溶劑移動速率較快</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>分液(傾析)</t>
+          <t>靜置後,倒出上層的油</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>密度分層</t>
+          <t>密度不同分層</t>
         </is>
       </c>
     </row>
@@ -1680,17 +1680,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>溶解過濾再蒸發</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>純化的溶劑(水)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>加水溶鹽→過濾→蒸發</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>水汽化冷凝、雜質留下</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>與濾紙作用弱、移動快</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1715,22 +1715,22 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>各成分移動速率不同</t>
+          <t>不溶固體/溶解固體/水</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>加水溶鹽→過濾→蒸發</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>不可浸入溶劑中</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
           <t>濾紙層析,各色素移動速率不同</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>不可浸入溶劑中</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>水汽化冷凝、雜質留下</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>蒸餾</t>
+          <t>鹽</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>漏斗與濾紙</t>
+          <t>蒸發結晶</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>蒸發結晶</t>
+          <t>過濾</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>純化的溶劑(水)</t>
+          <t>靜置後,倒出上層的油</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>與濾紙作用弱、移動快</t>
+          <t>加水溶鹽→過濾→蒸發</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>水汽化冷凝、雜質留下</t>
+          <t>不溶固體/溶解固體/水</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>加水溶鹽→過濾→蒸發</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>純化的溶劑(水)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>導電性低、沸點固定</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>與濾紙作用弱、移動快</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>純化的溶劑(水)</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1880,17 +1880,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>各成分移動速率不同</t>
+          <t>導電性低、沸點固定</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>與濾紙作用弱、移動快</t>
+          <t>純化的溶劑(水)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>不溶固體/溶解固體/水</t>
+          <t>加水溶鹽→過濾→蒸發</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">

--- a/02_加值成品/八上/八上2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>顆粒差異</t>
+          <t>顆粒差異：不溶於液體的固體顆粒比濾紙孔洞大，過不去而被擋住，液體則能通過，可用過濾分離</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>溶劑蒸發</t>
+          <t>溶劑蒸發：把海水加熱使水分蒸發，水分減少後鹽會逐漸結晶析出，這種方法叫蒸發結晶</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>汽化冷凝</t>
+          <t>汽化冷凝：不同液體沸點不同，先把混合液加熱使沸點較低的先汽化，再冷凝收集，可用蒸餾分離</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>移動速率差</t>
+          <t>移動速率差：不同色素分子隨溶劑在濾紙上移動的速率不同，會逐漸分開，可用濾紙層析分離</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>被擋住</t>
+          <t>被擋住：不溶於液體的固體顆粒比濾紙孔洞大，無法通過，會被擋在濾紙上</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>放熱：蒸氣遇冷失去熱量重新變回液體的過程稱為冷凝，這個過程會釋放熱量</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>日曬</t>
+          <t>日曬：利用太陽的熱能使海水中的水分自然蒸發，留下鹽分，這是蒸發法的應用</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>需蒸發</t>
+          <t>需蒸發：糖已經溶解在水中形成均勻的溶液，無法用過濾這種只能分離不溶固體的方法分開，必須改用蒸發結晶</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>器材</t>
+          <t>器材：過濾時用來隔開固體與液體的多孔紙張稱為濾紙，讓液體通過而固體被擋住</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>淡化</t>
+          <t>淡化：利用蒸餾或逆滲透等方法把海水中的鹽分去除、變成可飲用的淡水，這個過程稱為海水淡化</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>沙不溶</t>
+          <t>沙不溶：泥沙不溶於水，屬於不溶固體顆粒，比濾紙孔洞大會被擋住，可用過濾把泥沙和水分開</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>沸點不同</t>
+          <t>沸點不同：酒精沸點(約78℃)比水(100℃)低，加熱時酒精會先汽化，可用蒸餾法把兩者分開</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>水蒸發</t>
+          <t>水蒸發：鹽水加熱後水分持續蒸發逸散，鹽不會隨水蒸發，最後留下的固體就是鹽</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>冷凝液</t>
+          <t>冷凝液：蒸餾時先讓水汽化、再收集冷凝下來的液體，這個冷凝液是比較純淨的溶劑(水)，不含原本溶解在裡面的雜質</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>移動較快</t>
+          <t>移動較快：不同色素隨溶劑在濾紙上移動的速率不同，跑得比較遠代表這種色素隨溶劑移動的速率比較快</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>冷凝取水、殘留取鹽</t>
+          <t>冷凝取水、殘留取鹽：蒸餾時把汽化後冷凝收集到的液體當作純水，而留在原本容器裡沒有蒸發的固體就是鹽，可以同時得到兩者</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>基本組</t>
+          <t>基本組：過濾裝置最基本需要漏斗搭配濾紙，讓液體流過濾紙、固體顆粒被擋在濾紙上</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>汽化再凝</t>
+          <t>汽化再凝：海水淡化常利用讓海水汽化、再收集冷凝的純水這種原理，和蒸餾的原理相近</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>溶劑蒸發</t>
+          <t>溶劑蒸發：把糖水加熱使水分蒸發，水分減少後糖會逐漸結晶析出，這種方法叫蒸發結晶</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>汽化</t>
+          <t>汽化：蒸餾時先把液體加熱到沸點使其汽化變成蒸氣，再讓蒸氣冷卻凝結成純淨的液體收集起來</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>兩步驟</t>
+          <t>兩步驟：先加水把鹽溶解，沙不溶解；再用過濾把不溶的沙分離出來；最後把濾液加熱蒸發，讓水分蒸發後留下鹽，共需兩個步驟依序完成</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>分離沸點</t>
+          <t>分離沸點：蒸餾時只有水會汽化變成蒸氣，鹽等雜質沸點高不會跟著汽化，留在原容器中；把水蒸氣收集冷凝後就是不含雜質的純水</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>速率差</t>
+          <t>速率差：不同色素分子和濾紙、溶劑之間的作用力不同，隨溶劑移動的速率也不同，因此在濾紙上會逐漸分開呈現不同顏色的痕跡</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>密度不同分層</t>
+          <t>密度不同分層：油和水不互溶且密度不同，靜置後油會浮在上層、水在下層，把上層的油倒出來就能分離</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>逐步</t>
+          <t>逐步：先用過濾把不溶的固體分離出來，再把濾液加熱蒸發，讓水分蒸發後留下溶解的固體，依序就能把不溶固體、溶解固體、水這三者都分離出來</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>避免溶掉</t>
+          <t>避免溶掉：如果墨水點浸到溶劑裡，色素會直接溶解擴散到溶劑中而不會沿著濾紙往上跑，導致層析失敗，所以墨水點的位置要高於溶劑液面</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>沸點低先汽化</t>
+          <t>沸點低先汽化：加熱混合液時，沸點較低的酒精會先達到沸點汽化蒸出，水的沸點較高，會比較晚才汽化</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>性質檢驗</t>
+          <t>性質檢驗：蒸餾水幾乎不含雜質離子，導電性很低；純物質也有固定的沸點，可以用這兩項性質來檢驗蒸餾水是否夠純</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>層析</t>
+          <t>層析：不同色素分子在濾紙上隨溶劑移動的速率不同，會逐漸分開呈現不同顏色的痕跡，因此可以用濾紙層析法分析墨水含有哪些色素成分</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>步驟</t>
+          <t>步驟：先加水讓鹽溶解、沙不溶解，再用過濾把不溶的沙分離出來，最後把濾液加熱蒸發，讓水分蒸發後留下鹽，依序完成三者分離</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上2-3_三種難度測驗卷.xlsx
@@ -603,22 +603,22 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
+          <t>蒸餾</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>蒸發結晶</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
           <t>濾紙層析</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>蒸發結晶</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>不能</t>
-        </is>
-      </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>鹽</t>
+          <t>漏斗與濾紙</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>過濾</t>
+          <t>不溶固體</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>蒸餾</t>
+          <t>蒸發結晶</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>漏斗與濾紙</t>
+          <t>蒸發</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>漏斗與濾紙</t>
+          <t>蒸餾</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>蒸發結晶</t>
+          <t>液體受熱汽化</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>漏斗與濾紙</t>
+          <t>不溶固體</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>酒精</t>
+          <t>鹽</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1279,14 +1279,14 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>濾紙層析</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
           <t>過濾</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>酒精</t>
-        </is>
-      </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>漏斗與濾紙</t>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>蒸發結晶</t>
+          <t>不溶固體</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>冷凝</t>
+          <t>不溶固體</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
